--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251110_201557.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251110_201557.xlsx
@@ -4460,7 +4460,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251110_201557.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251110_201557.xlsx
@@ -4460,7 +4460,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251110_201557.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251110_201557.xlsx
@@ -5298,7 +5298,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251110_201557.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251110_201557.xlsx
@@ -7322,7 +7322,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251110_201557.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251110_201557.xlsx
@@ -7322,7 +7322,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251110_201557.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251110_201557.xlsx
@@ -4460,7 +4460,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251110_201557.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251110_201557.xlsx
@@ -4460,7 +4460,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251110_201557.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251110_201557.xlsx
@@ -4460,7 +4460,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251110_201557.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251110_201557.xlsx
@@ -4460,7 +4460,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251110_201557.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251110_201557.xlsx
@@ -4460,7 +4460,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251110_201557.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251110_201557.xlsx
@@ -4460,7 +4460,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251110_201557.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251110_201557.xlsx
@@ -4460,7 +4460,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
